--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cl948\OneDrive\GitHub\ccl_cv\cv_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E174210-476A-4138-ADDF-3429B85B632D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C245FB-7585-4B23-A84F-921B9C3F4EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="301">
   <si>
     <t>type</t>
   </si>
@@ -922,6 +922,12 @@
   </si>
   <si>
     <t>Associate Professor</t>
+  </si>
+  <si>
+    <t>Life-course processes as cause and effect of macro-level changes in gun violence</t>
+  </si>
+  <si>
+    <t>https://clanfear.github.io/ioc_2026-02-04/slides.html</t>
   </si>
 </sst>
 </file>
@@ -1315,18 +1321,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H146"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H147"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" customWidth="1"/>
-    <col min="2" max="2" width="57.54296875" customWidth="1"/>
-    <col min="3" max="4" width="9.1796875" style="5"/>
-    <col min="5" max="5" width="42.54296875" customWidth="1"/>
-    <col min="6" max="6" width="43.26953125" customWidth="1"/>
-    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.7890625" customWidth="1"/>
+    <col min="2" max="2" width="57.5234375" customWidth="1"/>
+    <col min="3" max="4" width="9.15625" style="5"/>
+    <col min="5" max="5" width="42.5234375" customWidth="1"/>
+    <col min="6" max="6" width="43.26171875" customWidth="1"/>
+    <col min="7" max="7" width="10.62890625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1352,7 +1358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1369,7 +1375,7 @@
         <v>43608</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1389,7 +1395,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1409,7 +1415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1429,7 +1435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1449,7 +1455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1469,7 +1475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1492,7 +1498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1515,7 +1521,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1532,7 +1538,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1549,7 +1555,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1566,7 +1572,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1580,7 +1586,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1597,7 +1603,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1614,7 +1620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1642,7 +1648,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1659,7 +1665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1676,7 +1682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1693,7 +1699,7 @@
         <v>42690</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1710,7 +1716,7 @@
         <v>42460</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1727,7 +1733,7 @@
         <v>41963</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1744,7 +1750,7 @@
         <v>41661</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1761,7 +1767,7 @@
         <v>42459</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1781,7 +1787,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -1801,7 +1807,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1821,7 +1827,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -1838,7 +1844,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1855,7 +1861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1872,7 +1878,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1889,7 +1895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1906,7 +1912,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1923,7 +1929,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -1940,7 +1946,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -1957,7 +1963,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1974,7 +1980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -1983,7 +1989,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -1997,7 +2003,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2014,7 +2020,7 @@
         <v>43783</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -2034,7 +2040,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2051,7 +2057,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2065,7 +2071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -2085,7 +2091,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2105,7 +2111,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2122,7 +2128,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -2139,7 +2145,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -2156,7 +2162,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -2176,7 +2182,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -2196,7 +2202,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -2210,7 +2216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>163</v>
       </c>
@@ -2227,7 +2233,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -2244,7 +2250,7 @@
         <v>43481</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2261,7 +2267,7 @@
         <v>42603</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2278,7 +2284,7 @@
         <v>42602</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2295,7 +2301,7 @@
         <v>44151</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -2312,7 +2318,7 @@
         <v>43398</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -2332,7 +2338,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2352,7 +2358,7 @@
         <v>43735</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -2360,7 +2366,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -2368,7 +2374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -2376,7 +2382,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>35</v>
       </c>
@@ -2396,7 +2402,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -2413,7 +2419,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -2430,7 +2436,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2447,7 +2453,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>35</v>
       </c>
@@ -2467,7 +2473,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -2475,7 +2481,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -2492,7 +2498,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>175</v>
       </c>
@@ -2509,7 +2515,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -2523,7 +2529,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -2531,7 +2537,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>47</v>
       </c>
@@ -2554,7 +2560,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -2577,7 +2583,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2594,7 +2600,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2611,7 +2617,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -2628,7 +2634,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>69</v>
       </c>
@@ -2636,7 +2642,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>69</v>
       </c>
@@ -2644,7 +2650,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>35</v>
       </c>
@@ -2664,7 +2670,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -2672,7 +2678,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>35</v>
       </c>
@@ -2689,7 +2695,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2706,7 +2712,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -2723,7 +2729,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>163</v>
       </c>
@@ -2740,7 +2746,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -2757,7 +2763,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -2774,7 +2780,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -2791,7 +2797,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -2808,7 +2814,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -2825,7 +2831,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>69</v>
       </c>
@@ -2833,7 +2839,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>69</v>
       </c>
@@ -2841,7 +2847,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -2861,7 +2867,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -2881,7 +2887,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>35</v>
       </c>
@@ -2901,7 +2907,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>35</v>
       </c>
@@ -2918,7 +2924,7 @@
         <v>45227</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>69</v>
       </c>
@@ -2926,7 +2932,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>69</v>
       </c>
@@ -2934,7 +2940,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2954,7 +2960,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -2974,7 +2980,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -2994,7 +3000,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -3014,7 +3020,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -3034,7 +3040,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>163</v>
       </c>
@@ -3051,7 +3057,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -3068,7 +3074,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>69</v>
       </c>
@@ -3076,7 +3082,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3096,7 +3102,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -3116,7 +3122,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>69</v>
       </c>
@@ -3124,7 +3130,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>69</v>
       </c>
@@ -3132,7 +3138,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>69</v>
       </c>
@@ -3140,7 +3146,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>44</v>
       </c>
@@ -3154,7 +3160,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -3174,7 +3180,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>69</v>
       </c>
@@ -3182,7 +3188,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>175</v>
       </c>
@@ -3193,7 +3199,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>69</v>
       </c>
@@ -3201,7 +3207,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -3221,7 +3227,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>69</v>
       </c>
@@ -3229,7 +3235,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -3249,7 +3255,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>69</v>
       </c>
@@ -3257,7 +3263,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>44</v>
       </c>
@@ -3274,7 +3280,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>163</v>
       </c>
@@ -3285,7 +3291,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>163</v>
       </c>
@@ -3296,7 +3302,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>163</v>
       </c>
@@ -3307,7 +3313,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>163</v>
       </c>
@@ -3318,7 +3324,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>163</v>
       </c>
@@ -3329,7 +3335,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>163</v>
       </c>
@@ -3340,7 +3346,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>163</v>
       </c>
@@ -3351,7 +3357,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -3362,7 +3368,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>69</v>
       </c>
@@ -3370,7 +3376,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -3390,7 +3396,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3410,7 +3416,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3430,7 +3436,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -3444,7 +3450,7 @@
         <v>45869</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -3464,7 +3470,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -3484,7 +3490,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -3501,7 +3507,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>163</v>
       </c>
@@ -3518,7 +3524,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -3532,7 +3538,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>44</v>
       </c>
@@ -3549,7 +3555,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>47</v>
       </c>
@@ -3572,7 +3578,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>47</v>
       </c>
@@ -3592,7 +3598,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>44</v>
       </c>
@@ -3609,7 +3615,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>44</v>
       </c>
@@ -3626,7 +3632,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>69</v>
       </c>
@@ -3634,7 +3640,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>69</v>
       </c>
@@ -3642,7 +3648,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>129</v>
       </c>
@@ -3657,6 +3663,26 @@
       </c>
       <c r="E146" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" t="s">
+        <v>299</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E147" t="s">
+        <v>138</v>
+      </c>
+      <c r="G147" s="1">
+        <v>46057</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3679,8 +3705,9 @@
     <hyperlink ref="H131" r:id="rId15" tooltip="Original URL: https://clanfear.github.io/mopac_2025-06-26/slides.html. Click or tap if you trust this link." display="https://eur03.safelinks.protection.outlook.com/?url=https%3A%2F%2Fclanfear.github.io%2Fmopac_2025-06-26%2Fslides.html&amp;data=05%7C02%7Ccl948%40universityofcambridgecloud.onmicrosoft.com%7C1be3785cf33946248ca708ddb9476c34%7C49a50445bdfa4b79ade3547b4f3986e9%7C1%7C0%7C638870438613963179%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=L9SUxhel%2FhX8IJVvyZiUFegsak%2BVybEyEYWBwqRrJJA%3D&amp;reserved=0" xr:uid="{1E85D9FE-EB84-44E3-A01C-C10B0360C69A}"/>
     <hyperlink ref="H140" r:id="rId16" xr:uid="{A272E62B-FD9F-4AC9-A289-80E6110700B3}"/>
     <hyperlink ref="H141" r:id="rId17" xr:uid="{4DFB1F65-9DA4-4605-81E1-2FC00769EF0A}"/>
+    <hyperlink ref="H147" r:id="rId18" xr:uid="{E204F4EF-E996-4D19-B6F3-679BA3B88CEB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cl948\OneDrive\GitHub\ccl_cv\cv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C245FB-7585-4B23-A84F-921B9C3F4EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4458CE0-70C0-41BA-8CDE-7707A06E7C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
+    <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="303">
   <si>
     <t>type</t>
   </si>
@@ -928,6 +928,12 @@
   </si>
   <si>
     <t>https://clanfear.github.io/ioc_2026-02-04/slides.html</t>
+  </si>
+  <si>
+    <t>*British Journal of Criminology*</t>
+  </si>
+  <si>
+    <t>Editorial Board</t>
   </si>
 </sst>
 </file>
@@ -1321,18 +1327,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H147"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:H148"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.7890625" customWidth="1"/>
-    <col min="2" max="2" width="57.5234375" customWidth="1"/>
-    <col min="3" max="4" width="9.15625" style="5"/>
-    <col min="5" max="5" width="42.5234375" customWidth="1"/>
-    <col min="6" max="6" width="43.26171875" customWidth="1"/>
-    <col min="7" max="7" width="10.62890625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+    <col min="2" max="2" width="57.54296875" customWidth="1"/>
+    <col min="3" max="4" width="9.1796875" style="5"/>
+    <col min="5" max="5" width="42.54296875" customWidth="1"/>
+    <col min="6" max="6" width="43.26953125" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1358,7 +1364,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1375,7 +1381,7 @@
         <v>43608</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1395,7 +1401,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1415,7 +1421,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1435,7 +1441,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1455,7 +1461,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1475,7 +1481,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1498,7 +1504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1521,7 +1527,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1538,7 +1544,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1555,7 +1561,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1572,7 +1578,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1586,7 +1592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1603,7 +1609,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1620,7 +1626,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1634,7 +1640,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1648,7 +1654,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1665,7 +1671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1682,7 +1688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1699,7 +1705,7 @@
         <v>42690</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1716,7 +1722,7 @@
         <v>42460</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1733,7 +1739,7 @@
         <v>41963</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1756,7 @@
         <v>41661</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1767,7 +1773,7 @@
         <v>42459</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1787,7 +1793,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -1807,7 +1813,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1827,7 +1833,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -1844,7 +1850,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1861,7 +1867,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1878,7 +1884,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1895,7 +1901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1912,7 +1918,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1929,7 +1935,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -1946,7 +1952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -1963,7 +1969,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1980,7 +1986,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -1989,7 +1995,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -2003,7 +2009,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2020,7 +2026,7 @@
         <v>43783</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -2040,7 +2046,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2057,7 +2063,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2071,7 +2077,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -2091,7 +2097,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2111,7 +2117,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2128,7 +2134,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -2145,7 +2151,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -2162,7 +2168,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -2182,7 +2188,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -2202,7 +2208,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -2216,7 +2222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>163</v>
       </c>
@@ -2233,7 +2239,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -2250,7 +2256,7 @@
         <v>43481</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2267,7 +2273,7 @@
         <v>42603</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2284,7 +2290,7 @@
         <v>42602</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2301,7 +2307,7 @@
         <v>44151</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -2318,7 +2324,7 @@
         <v>43398</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -2338,7 +2344,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2358,7 +2364,7 @@
         <v>43735</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -2366,7 +2372,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -2374,7 +2380,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -2382,7 +2388,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>35</v>
       </c>
@@ -2402,7 +2408,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -2419,7 +2425,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -2436,7 +2442,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2453,7 +2459,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>35</v>
       </c>
@@ -2473,7 +2479,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -2481,7 +2487,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -2498,7 +2504,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>175</v>
       </c>
@@ -2515,7 +2521,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -2529,7 +2535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -2537,7 +2543,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>47</v>
       </c>
@@ -2560,7 +2566,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -2583,7 +2589,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2600,7 +2606,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2617,7 +2623,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -2634,7 +2640,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>69</v>
       </c>
@@ -2642,7 +2648,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>69</v>
       </c>
@@ -2650,7 +2656,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>35</v>
       </c>
@@ -2670,7 +2676,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -2678,7 +2684,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>35</v>
       </c>
@@ -2695,7 +2701,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2712,7 +2718,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -2729,7 +2735,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>163</v>
       </c>
@@ -2746,7 +2752,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -2763,7 +2769,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -2780,7 +2786,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -2797,7 +2803,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -2814,7 +2820,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -2831,7 +2837,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>69</v>
       </c>
@@ -2839,7 +2845,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>69</v>
       </c>
@@ -2847,7 +2853,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -2867,7 +2873,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -2887,7 +2893,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>35</v>
       </c>
@@ -2907,7 +2913,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>35</v>
       </c>
@@ -2924,7 +2930,7 @@
         <v>45227</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>69</v>
       </c>
@@ -2932,7 +2938,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>69</v>
       </c>
@@ -2940,7 +2946,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2960,7 +2966,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -2980,7 +2986,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -3000,7 +3006,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -3020,7 +3026,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -3040,7 +3046,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>163</v>
       </c>
@@ -3057,7 +3063,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -3074,7 +3080,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>69</v>
       </c>
@@ -3082,7 +3088,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3102,7 +3108,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -3122,7 +3128,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>69</v>
       </c>
@@ -3130,7 +3136,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>69</v>
       </c>
@@ -3138,7 +3144,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>69</v>
       </c>
@@ -3146,7 +3152,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>44</v>
       </c>
@@ -3160,7 +3166,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -3180,7 +3186,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>69</v>
       </c>
@@ -3188,18 +3194,24 @@
         <v>247</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>175</v>
       </c>
       <c r="B114" t="s">
         <v>248</v>
       </c>
+      <c r="C114" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="E114" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>69</v>
       </c>
@@ -3207,7 +3219,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -3227,7 +3239,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>69</v>
       </c>
@@ -3235,7 +3247,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -3255,7 +3267,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>69</v>
       </c>
@@ -3263,7 +3275,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>44</v>
       </c>
@@ -3280,7 +3292,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>163</v>
       </c>
@@ -3291,7 +3303,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>163</v>
       </c>
@@ -3302,7 +3314,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>163</v>
       </c>
@@ -3313,7 +3325,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>163</v>
       </c>
@@ -3324,7 +3336,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>163</v>
       </c>
@@ -3335,7 +3347,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>163</v>
       </c>
@@ -3346,7 +3358,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>163</v>
       </c>
@@ -3357,7 +3369,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -3368,7 +3380,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>69</v>
       </c>
@@ -3376,7 +3388,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -3396,7 +3408,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3416,7 +3428,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3436,7 +3448,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -3450,7 +3462,7 @@
         <v>45869</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -3470,7 +3482,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -3490,7 +3502,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -3507,7 +3519,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>163</v>
       </c>
@@ -3524,7 +3536,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -3538,7 +3550,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>44</v>
       </c>
@@ -3555,7 +3567,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>47</v>
       </c>
@@ -3578,7 +3590,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>47</v>
       </c>
@@ -3598,7 +3610,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>44</v>
       </c>
@@ -3615,7 +3627,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>44</v>
       </c>
@@ -3632,7 +3644,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>69</v>
       </c>
@@ -3640,7 +3652,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>69</v>
       </c>
@@ -3648,7 +3660,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>129</v>
       </c>
@@ -3665,7 +3677,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -3683,6 +3695,23 @@
       </c>
       <c r="H147" s="2" t="s">
         <v>300</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>44</v>
+      </c>
+      <c r="B148" t="s">
+        <v>302</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E148" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cl948\OneDrive\GitHub\ccl_cv\cv_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4458CE0-70C0-41BA-8CDE-7707A06E7C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E4458CE0-70C0-41BA-8CDE-7707A06E7C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBEE2125-4AF2-433C-BB28-DECAB633FA10}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="7980" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
+    <workbookView xWindow="5190" yWindow="2910" windowWidth="28800" windowHeight="15345" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="301">
   <si>
     <t>type</t>
   </si>
@@ -544,12 +544,6 @@
   </si>
   <si>
     <t>Risk Assessment Committee</t>
-  </si>
-  <si>
-    <t>Associate Member</t>
-  </si>
-  <si>
-    <t>Aug 2022</t>
   </si>
   <si>
     <t>affiliation</t>
@@ -1327,18 +1321,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H148"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H147"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" customWidth="1"/>
-    <col min="2" max="2" width="57.54296875" customWidth="1"/>
-    <col min="3" max="4" width="9.1796875" style="5"/>
-    <col min="5" max="5" width="42.54296875" customWidth="1"/>
-    <col min="6" max="6" width="43.26953125" customWidth="1"/>
-    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="57.5703125" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="5"/>
+    <col min="5" max="5" width="42.5703125" customWidth="1"/>
+    <col min="6" max="6" width="43.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1364,7 +1358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1381,7 +1375,7 @@
         <v>43608</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1401,7 +1395,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1421,7 +1415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1441,7 +1435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1461,18 +1455,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C7" s="5">
         <v>2018</v>
       </c>
       <c r="E7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G7" s="1">
         <v>43399</v>
@@ -1481,7 +1475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1504,7 +1498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1527,7 +1521,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1544,7 +1538,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1561,7 +1555,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1578,7 +1572,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1592,7 +1586,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1609,7 +1603,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1626,7 +1620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1640,7 +1634,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1654,7 +1648,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1671,7 +1665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1688,29 +1682,29 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C20" s="5">
         <v>2016</v>
       </c>
       <c r="E20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G20" s="1">
         <v>42690</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C21" s="5">
         <v>2016</v>
@@ -1722,29 +1716,29 @@
         <v>42460</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C22" s="5">
         <v>2014</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G22" s="1">
         <v>41963</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C23" s="5">
         <v>2014</v>
@@ -1756,7 +1750,7 @@
         <v>41661</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1773,7 +1767,7 @@
         <v>42459</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1793,7 +1787,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -1813,7 +1807,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1833,12 +1827,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C28" s="5">
         <v>2018</v>
@@ -1850,12 +1844,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C29" s="5">
         <v>2015</v>
@@ -1867,7 +1861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1884,7 +1878,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1901,7 +1895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1918,7 +1912,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1935,7 +1929,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -1952,7 +1946,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -1969,7 +1963,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1986,7 +1980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -1995,7 +1989,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -2009,24 +2003,24 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>72</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G39" s="1">
         <v>43783</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -2046,7 +2040,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2063,7 +2057,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2077,7 +2071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -2097,7 +2091,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2117,7 +2111,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2134,7 +2128,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -2151,7 +2145,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -2168,7 +2162,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -2188,7 +2182,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -2208,7 +2202,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -2222,7 +2216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>163</v>
       </c>
@@ -2239,75 +2233,75 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>8</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>72</v>
       </c>
       <c r="E52" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G52" s="1">
         <v>43481</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G53" s="1">
         <v>42603</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G54" s="1">
         <v>42602</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>81</v>
       </c>
       <c r="E55" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G55" s="1">
         <v>44151</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -2324,7 +2318,7 @@
         <v>43398</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -2344,18 +2338,18 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>72</v>
       </c>
       <c r="E58" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F58" t="s">
         <v>112</v>
@@ -2364,7 +2358,7 @@
         <v>43735</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -2372,7 +2366,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -2380,7 +2374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -2388,7 +2382,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>35</v>
       </c>
@@ -2408,7 +2402,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -2425,7 +2419,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -2442,7 +2436,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2459,7 +2453,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>35</v>
       </c>
@@ -2479,7 +2473,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -2487,7 +2481,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -2498,15 +2492,15 @@
         <v>134</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E68" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B69" t="s">
         <v>139</v>
@@ -2521,7 +2515,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -2535,7 +2529,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -2543,7 +2537,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>47</v>
       </c>
@@ -2554,19 +2548,19 @@
         <v>134</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E72" t="s">
         <v>150</v>
       </c>
       <c r="F72" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H72" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -2577,70 +2571,70 @@
         <v>134</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E73" t="s">
         <v>150</v>
       </c>
       <c r="F73" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H73" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>134</v>
       </c>
       <c r="E74" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G74" s="1">
         <v>44826</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>134</v>
       </c>
       <c r="E75" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G75" s="1">
         <v>44883</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>134</v>
       </c>
       <c r="E76" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G76" s="1">
         <v>44826</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>69</v>
       </c>
@@ -2648,7 +2642,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>69</v>
       </c>
@@ -2656,7 +2650,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>35</v>
       </c>
@@ -2676,7 +2670,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -2684,12 +2678,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>35</v>
       </c>
       <c r="B81" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E81" t="s">
         <v>161</v>
@@ -2701,7 +2695,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2718,7 +2712,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -2735,7 +2729,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>163</v>
       </c>
@@ -2752,7 +2746,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -2769,7 +2763,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -2786,24 +2780,24 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>44</v>
       </c>
       <c r="B87" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>158</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E87" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -2820,117 +2814,117 @@
         <v>138</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>173</v>
+        <v>300</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>174</v>
+        <v>295</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E89" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>69</v>
       </c>
       <c r="B90" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>69</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>158</v>
       </c>
       <c r="E92" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G92" s="1">
         <v>45177</v>
       </c>
       <c r="H92" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>158</v>
       </c>
       <c r="E93" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G93" s="1">
         <v>45245</v>
       </c>
       <c r="H93" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>35</v>
       </c>
       <c r="B94" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>158</v>
       </c>
       <c r="E94" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G94" s="1">
         <v>45124</v>
       </c>
       <c r="H94" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>35</v>
       </c>
       <c r="B95" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>158</v>
       </c>
       <c r="E95" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G95" s="1">
         <v>45227</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>69</v>
       </c>
@@ -2938,120 +2932,120 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E98" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G98" s="1">
         <v>45429</v>
       </c>
       <c r="H98" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E99" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G99" s="1">
         <v>45442</v>
       </c>
       <c r="H99" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E100" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G100" s="1">
         <v>45548</v>
       </c>
       <c r="H100" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E101" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G101" s="1">
         <v>45548</v>
       </c>
       <c r="H101" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E102" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G102" s="1">
         <v>45482</v>
       </c>
       <c r="H102" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>163</v>
       </c>
       <c r="B103" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>53</v>
@@ -3060,171 +3054,171 @@
         <v>150</v>
       </c>
       <c r="F103" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E104" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G104" s="1">
         <v>45589</v>
       </c>
       <c r="H104" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>69</v>
       </c>
       <c r="B105" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E106" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G106" s="1">
         <v>45611</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E107" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G107" s="1">
         <v>45636</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>69</v>
       </c>
       <c r="B108" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>69</v>
       </c>
       <c r="B109" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>69</v>
       </c>
       <c r="B110" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>44</v>
       </c>
       <c r="B111" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E111" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E112" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G112" s="1">
         <v>45764</v>
       </c>
       <c r="H112" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>69</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B114" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E114" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>69</v>
       </c>
       <c r="B115" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>158</v>
@@ -3236,54 +3230,54 @@
         <v>44945</v>
       </c>
       <c r="H116" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E118" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G118" s="1">
         <v>45878</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>69</v>
       </c>
       <c r="B119" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>44</v>
       </c>
       <c r="B120" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>53</v>
@@ -3292,205 +3286,205 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>163</v>
       </c>
       <c r="B121" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>163</v>
       </c>
       <c r="B122" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>163</v>
       </c>
       <c r="B123" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>163</v>
       </c>
       <c r="B124" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>163</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>163</v>
       </c>
       <c r="B126" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>163</v>
       </c>
       <c r="B127" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>163</v>
       </c>
       <c r="B128" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>69</v>
       </c>
       <c r="B129" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E130" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G130" s="1">
         <v>45904</v>
       </c>
       <c r="H130" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E131" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G131" s="1">
         <v>45834</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E132" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G132" s="1">
         <v>45927</v>
       </c>
       <c r="H132" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E133" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G133" s="1">
         <v>45869</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E134" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G134" s="1">
         <v>45967</v>
       </c>
       <c r="H134" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E135" t="s">
         <v>138</v>
@@ -3499,15 +3493,15 @@
         <v>45952</v>
       </c>
       <c r="H135" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>163</v>
       </c>
       <c r="B136" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>53</v>
@@ -3516,15 +3510,15 @@
         <v>150</v>
       </c>
       <c r="F136" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>163</v>
       </c>
       <c r="B137" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>53</v>
@@ -3533,32 +3527,32 @@
         <v>150</v>
       </c>
       <c r="F137" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>24</v>
       </c>
       <c r="B138" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E138" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>44</v>
       </c>
       <c r="B139" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>53</v>
@@ -3567,38 +3561,38 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>47</v>
       </c>
       <c r="B140" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>134</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E140" t="s">
         <v>150</v>
       </c>
       <c r="F140" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>47</v>
       </c>
       <c r="B141" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E141" t="s">
         <v>150</v>
@@ -3607,18 +3601,18 @@
         <v>49</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>44</v>
       </c>
       <c r="B142" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>53</v>
@@ -3627,48 +3621,48 @@
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>44</v>
       </c>
       <c r="B143" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E143" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>69</v>
       </c>
       <c r="B144" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>69</v>
       </c>
       <c r="B145" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>129</v>
       </c>
       <c r="B146" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>53</v>
@@ -3677,15 +3671,15 @@
         <v>138</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E147" t="s">
         <v>138</v>
@@ -3694,24 +3688,7 @@
         <v>46057</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>44</v>
-      </c>
-      <c r="B148" t="s">
-        <v>302</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E148" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E4458CE0-70C0-41BA-8CDE-7707A06E7C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBEE2125-4AF2-433C-BB28-DECAB633FA10}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258ADCEA-C5A4-4347-9470-6B860DDF8DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5190" yWindow="2910" windowWidth="28800" windowHeight="15345" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="302">
   <si>
     <t>type</t>
   </si>
@@ -928,6 +928,9 @@
   </si>
   <si>
     <t>Editorial Board</t>
+  </si>
+  <si>
+    <t>https://clanfear.github.io/CSSS_2026-04-15/slides.html</t>
   </si>
 </sst>
 </file>
@@ -1321,18 +1324,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H148"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="57.5703125" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="5"/>
-    <col min="5" max="5" width="42.5703125" customWidth="1"/>
-    <col min="6" max="6" width="43.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.83984375" customWidth="1"/>
+    <col min="2" max="2" width="57.578125" customWidth="1"/>
+    <col min="3" max="4" width="9.15625" style="5"/>
+    <col min="5" max="5" width="42.578125" customWidth="1"/>
+    <col min="6" max="6" width="43.26171875" customWidth="1"/>
+    <col min="7" max="7" width="10.578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1358,7 +1361,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>43608</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1395,7 +1398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1415,7 +1418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1455,7 +1458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1475,7 +1478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1498,7 +1501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1521,7 +1524,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1538,7 +1541,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1555,7 +1558,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1572,7 +1575,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1586,7 +1589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1620,7 +1623,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1634,7 +1637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1665,7 +1668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1682,7 +1685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>42690</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>42460</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1733,7 +1736,7 @@
         <v>41963</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>41661</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1767,7 +1770,7 @@
         <v>42459</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1787,7 +1790,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -1807,7 +1810,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1827,7 +1830,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -1844,7 +1847,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1861,7 +1864,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1878,7 +1881,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1895,7 +1898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1912,7 +1915,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1929,7 +1932,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -1946,7 +1949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -1963,7 +1966,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1980,7 +1983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -1989,7 +1992,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -2003,7 +2006,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2020,7 +2023,7 @@
         <v>43783</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -2040,7 +2043,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2057,7 +2060,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2071,7 +2074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -2091,7 +2094,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2111,7 +2114,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2128,7 +2131,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -2145,7 +2148,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -2182,7 +2185,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -2202,7 +2205,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -2216,7 +2219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>163</v>
       </c>
@@ -2233,7 +2236,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="15.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -2250,7 +2253,7 @@
         <v>43481</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2267,7 +2270,7 @@
         <v>42603</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2284,7 +2287,7 @@
         <v>42602</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2301,7 +2304,7 @@
         <v>44151</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -2318,7 +2321,7 @@
         <v>43398</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -2338,7 +2341,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2358,7 +2361,7 @@
         <v>43735</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -2366,7 +2369,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -2382,7 +2385,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>35</v>
       </c>
@@ -2402,7 +2405,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -2419,7 +2422,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -2436,7 +2439,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2453,7 +2456,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>35</v>
       </c>
@@ -2473,7 +2476,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -2498,7 +2501,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>173</v>
       </c>
@@ -2515,7 +2518,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -2529,7 +2532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -2537,7 +2540,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>47</v>
       </c>
@@ -2560,7 +2563,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -2583,7 +2586,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2600,7 +2603,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2617,7 +2620,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -2634,7 +2637,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>69</v>
       </c>
@@ -2642,7 +2645,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>69</v>
       </c>
@@ -2650,7 +2653,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>35</v>
       </c>
@@ -2670,7 +2673,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -2678,7 +2681,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>35</v>
       </c>
@@ -2695,7 +2698,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2712,7 +2715,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -2729,7 +2732,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>163</v>
       </c>
@@ -2746,7 +2749,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -2763,7 +2766,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -2780,7 +2783,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -2797,7 +2800,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -2814,7 +2817,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>44</v>
       </c>
@@ -2831,7 +2834,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>69</v>
       </c>
@@ -2839,7 +2842,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>69</v>
       </c>
@@ -2847,7 +2850,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -2867,7 +2870,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -2887,7 +2890,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>35</v>
       </c>
@@ -2907,7 +2910,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>35</v>
       </c>
@@ -2924,7 +2927,7 @@
         <v>45227</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>69</v>
       </c>
@@ -2932,7 +2935,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>69</v>
       </c>
@@ -2940,7 +2943,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -2980,7 +2983,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -3000,7 +3003,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -3020,7 +3023,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -3040,7 +3043,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>163</v>
       </c>
@@ -3057,7 +3060,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -3074,7 +3077,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>69</v>
       </c>
@@ -3082,7 +3085,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3102,7 +3105,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -3122,7 +3125,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>69</v>
       </c>
@@ -3130,7 +3133,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>69</v>
       </c>
@@ -3138,7 +3141,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>69</v>
       </c>
@@ -3146,7 +3149,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>44</v>
       </c>
@@ -3160,7 +3163,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -3180,7 +3183,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>69</v>
       </c>
@@ -3188,7 +3191,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>173</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>69</v>
       </c>
@@ -3213,7 +3216,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -3233,7 +3236,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>69</v>
       </c>
@@ -3241,7 +3244,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -3261,7 +3264,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>69</v>
       </c>
@@ -3269,7 +3272,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>44</v>
       </c>
@@ -3286,7 +3289,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>163</v>
       </c>
@@ -3297,7 +3300,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>163</v>
       </c>
@@ -3308,7 +3311,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>163</v>
       </c>
@@ -3319,7 +3322,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>163</v>
       </c>
@@ -3330,7 +3333,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>163</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>163</v>
       </c>
@@ -3352,7 +3355,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>163</v>
       </c>
@@ -3363,7 +3366,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -3374,7 +3377,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>69</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -3402,7 +3405,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3422,7 +3425,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3442,7 +3445,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -3456,7 +3459,7 @@
         <v>45869</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -3476,7 +3479,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -3496,7 +3499,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -3513,7 +3516,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>163</v>
       </c>
@@ -3530,7 +3533,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -3544,7 +3547,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>44</v>
       </c>
@@ -3561,7 +3564,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>47</v>
       </c>
@@ -3584,7 +3587,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>47</v>
       </c>
@@ -3604,7 +3607,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>44</v>
       </c>
@@ -3621,7 +3624,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>44</v>
       </c>
@@ -3638,7 +3641,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>69</v>
       </c>
@@ -3646,7 +3649,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>69</v>
       </c>
@@ -3654,7 +3657,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>129</v>
       </c>
@@ -3671,7 +3674,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -3689,6 +3692,26 @@
       </c>
       <c r="H147" s="2" t="s">
         <v>298</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148" t="s">
+        <v>212</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E148" t="s">
+        <v>113</v>
+      </c>
+      <c r="G148" s="1">
+        <v>46127</v>
+      </c>
+      <c r="H148" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cl948\OneDrive\GitHub\ccl_cv\cv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258ADCEA-C5A4-4347-9470-6B860DDF8DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F29D48-EE52-4DBE-AFBB-FA2750139283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="308">
   <si>
     <t>type</t>
   </si>
@@ -931,6 +931,24 @@
   </si>
   <si>
     <t>https://clanfear.github.io/CSSS_2026-04-15/slides.html</t>
+  </si>
+  <si>
+    <t>Max Planck Institute for the Study of Crime, Security and Law</t>
+  </si>
+  <si>
+    <t>https://clanfear.github.io/mpi_2026-05-07/slides.html</t>
+  </si>
+  <si>
+    <t>Policing, the life course, and social change: Recent research and new questions</t>
+  </si>
+  <si>
+    <t>https://clanfear.github.io/manchester_2026-03-23/slides.html</t>
+  </si>
+  <si>
+    <t>*Policing and the Life Course Workshop*, University of Manchester</t>
+  </si>
+  <si>
+    <t>Criminology &amp; Public Policy</t>
   </si>
 </sst>
 </file>
@@ -1324,18 +1342,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H148"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:H151"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.83984375" customWidth="1"/>
-    <col min="2" max="2" width="57.578125" customWidth="1"/>
-    <col min="3" max="4" width="9.15625" style="5"/>
-    <col min="5" max="5" width="42.578125" customWidth="1"/>
-    <col min="6" max="6" width="43.26171875" customWidth="1"/>
-    <col min="7" max="7" width="10.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+    <col min="2" max="2" width="57.54296875" customWidth="1"/>
+    <col min="3" max="4" width="9.1796875" style="5"/>
+    <col min="5" max="5" width="42.54296875" customWidth="1"/>
+    <col min="6" max="6" width="43.26953125" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1361,7 +1379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1378,7 +1396,7 @@
         <v>43608</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1398,7 +1416,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1418,7 +1436,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1438,7 +1456,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1458,7 +1476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1478,7 +1496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1501,7 +1519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1524,7 +1542,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1541,7 +1559,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1558,7 +1576,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1575,7 +1593,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1589,7 +1607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1606,7 +1624,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1623,7 +1641,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1637,7 +1655,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1651,7 +1669,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1668,7 +1686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1685,7 +1703,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1702,7 +1720,7 @@
         <v>42690</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1719,7 +1737,7 @@
         <v>42460</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1736,7 +1754,7 @@
         <v>41963</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1753,7 +1771,7 @@
         <v>41661</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1770,7 +1788,7 @@
         <v>42459</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1790,7 +1808,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -1810,7 +1828,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1830,7 +1848,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -1847,7 +1865,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1864,7 +1882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1881,7 +1899,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1898,7 +1916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1915,7 +1933,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1932,7 +1950,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -1949,7 +1967,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -1966,7 +1984,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1983,7 +2001,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -1992,7 +2010,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -2006,7 +2024,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2023,7 +2041,7 @@
         <v>43783</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -2043,7 +2061,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2060,7 +2078,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2074,7 +2092,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -2094,7 +2112,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2114,7 +2132,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2131,7 +2149,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -2148,7 +2166,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -2165,7 +2183,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -2185,7 +2203,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -2205,7 +2223,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -2219,7 +2237,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>163</v>
       </c>
@@ -2236,7 +2254,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -2253,7 +2271,7 @@
         <v>43481</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2270,7 +2288,7 @@
         <v>42603</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2287,7 +2305,7 @@
         <v>42602</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2304,7 +2322,7 @@
         <v>44151</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -2321,7 +2339,7 @@
         <v>43398</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -2341,7 +2359,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2361,7 +2379,7 @@
         <v>43735</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -2369,7 +2387,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -2377,7 +2395,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -2385,7 +2403,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>35</v>
       </c>
@@ -2405,7 +2423,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -2422,7 +2440,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -2439,7 +2457,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2456,7 +2474,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>35</v>
       </c>
@@ -2476,7 +2494,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -2484,7 +2502,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -2501,7 +2519,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>173</v>
       </c>
@@ -2518,7 +2536,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -2532,7 +2550,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -2540,7 +2558,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>47</v>
       </c>
@@ -2563,7 +2581,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -2586,7 +2604,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2603,7 +2621,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2620,7 +2638,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -2637,7 +2655,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>69</v>
       </c>
@@ -2645,7 +2663,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>69</v>
       </c>
@@ -2653,7 +2671,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>35</v>
       </c>
@@ -2673,7 +2691,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -2681,7 +2699,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>35</v>
       </c>
@@ -2698,7 +2716,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2715,7 +2733,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -2732,7 +2750,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>163</v>
       </c>
@@ -2749,7 +2767,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -2766,7 +2784,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -2783,7 +2801,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -2800,7 +2818,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -2817,7 +2835,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>44</v>
       </c>
@@ -2834,7 +2852,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>69</v>
       </c>
@@ -2842,7 +2860,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>69</v>
       </c>
@@ -2850,7 +2868,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -2870,7 +2888,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -2890,7 +2908,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>35</v>
       </c>
@@ -2910,7 +2928,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>35</v>
       </c>
@@ -2927,7 +2945,7 @@
         <v>45227</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>69</v>
       </c>
@@ -2935,7 +2953,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>69</v>
       </c>
@@ -2943,7 +2961,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2963,7 +2981,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -2983,7 +3001,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -3003,7 +3021,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -3023,7 +3041,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -3043,7 +3061,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>163</v>
       </c>
@@ -3060,7 +3078,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -3077,7 +3095,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>69</v>
       </c>
@@ -3085,7 +3103,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3105,7 +3123,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -3125,7 +3143,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>69</v>
       </c>
@@ -3133,7 +3151,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>69</v>
       </c>
@@ -3141,7 +3159,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>69</v>
       </c>
@@ -3149,7 +3167,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>44</v>
       </c>
@@ -3163,7 +3181,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -3183,7 +3201,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>69</v>
       </c>
@@ -3191,7 +3209,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>173</v>
       </c>
@@ -3208,7 +3226,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>69</v>
       </c>
@@ -3216,7 +3234,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -3236,7 +3254,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>69</v>
       </c>
@@ -3244,7 +3262,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -3264,7 +3282,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>69</v>
       </c>
@@ -3272,7 +3290,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>44</v>
       </c>
@@ -3289,7 +3307,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>163</v>
       </c>
@@ -3300,7 +3318,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>163</v>
       </c>
@@ -3311,7 +3329,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>163</v>
       </c>
@@ -3322,7 +3340,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>163</v>
       </c>
@@ -3333,7 +3351,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>163</v>
       </c>
@@ -3344,7 +3362,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>163</v>
       </c>
@@ -3355,7 +3373,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>163</v>
       </c>
@@ -3366,7 +3384,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -3377,7 +3395,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>69</v>
       </c>
@@ -3385,7 +3403,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -3405,7 +3423,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3425,7 +3443,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3445,7 +3463,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -3459,7 +3477,7 @@
         <v>45869</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -3479,7 +3497,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -3499,7 +3517,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -3516,7 +3534,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>163</v>
       </c>
@@ -3533,7 +3551,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -3547,7 +3565,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>44</v>
       </c>
@@ -3564,7 +3582,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>47</v>
       </c>
@@ -3587,7 +3605,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>47</v>
       </c>
@@ -3607,7 +3625,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>44</v>
       </c>
@@ -3624,7 +3642,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>44</v>
       </c>
@@ -3641,7 +3659,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>69</v>
       </c>
@@ -3649,7 +3667,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>69</v>
       </c>
@@ -3657,7 +3675,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>129</v>
       </c>
@@ -3674,7 +3692,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -3694,7 +3712,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -3712,6 +3730,54 @@
       </c>
       <c r="H148" t="s">
         <v>301</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149" t="s">
+        <v>297</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E149" t="s">
+        <v>302</v>
+      </c>
+      <c r="G149" s="1">
+        <v>46149</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150" t="s">
+        <v>304</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E150" t="s">
+        <v>306</v>
+      </c>
+      <c r="G150" s="1">
+        <v>46104</v>
+      </c>
+      <c r="H150" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>69</v>
+      </c>
+      <c r="B151" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3735,8 +3801,9 @@
     <hyperlink ref="H140" r:id="rId16" xr:uid="{A272E62B-FD9F-4AC9-A289-80E6110700B3}"/>
     <hyperlink ref="H141" r:id="rId17" xr:uid="{4DFB1F65-9DA4-4605-81E1-2FC00769EF0A}"/>
     <hyperlink ref="H147" r:id="rId18" xr:uid="{E204F4EF-E996-4D19-B6F3-679BA3B88CEB}"/>
+    <hyperlink ref="H149" r:id="rId19" xr:uid="{C8F5A46F-F604-4371-989F-066614572D5D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId20"/>
 </worksheet>
 </file>
--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cl948\OneDrive\GitHub\ccl_cv\cv_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F29D48-EE52-4DBE-AFBB-FA2750139283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C4FDA76-7522-4407-9B60-216AB26505CF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
+    <workbookView xWindow="-21720" yWindow="-11745" windowWidth="21840" windowHeight="37920" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="313">
   <si>
     <t>type</t>
   </si>
@@ -949,6 +949,21 @@
   </si>
   <si>
     <t>Criminology &amp; Public Policy</t>
+  </si>
+  <si>
+    <t>*Meeting of Commissioners and Academics: Economics of Modern Slavery and Human Trafficking*, Nuffield College</t>
+  </si>
+  <si>
+    <t>Relationships and opportunities in exploitation (w/' Zora Hauser)</t>
+  </si>
+  <si>
+    <t>Crime Science</t>
+  </si>
+  <si>
+    <t>Journal of Criminal Justice</t>
+  </si>
+  <si>
+    <t>Declan Sullivan</t>
   </si>
 </sst>
 </file>
@@ -1043,6 +1058,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1342,18 +1361,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H151"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H155"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" customWidth="1"/>
-    <col min="2" max="2" width="57.54296875" customWidth="1"/>
-    <col min="3" max="4" width="9.1796875" style="5"/>
-    <col min="5" max="5" width="42.54296875" customWidth="1"/>
-    <col min="6" max="6" width="43.26953125" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="57.5703125" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="5"/>
+    <col min="5" max="5" width="42.5703125" customWidth="1"/>
+    <col min="6" max="6" width="43.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1379,7 +1398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1396,7 +1415,7 @@
         <v>43608</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1416,7 +1435,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1436,7 +1455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1456,7 +1475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1476,7 +1495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1496,7 +1515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1519,7 +1538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1542,7 +1561,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1559,7 +1578,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1576,7 +1595,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1593,7 +1612,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1607,7 +1626,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1624,7 +1643,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1641,7 +1660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1655,7 +1674,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1669,7 +1688,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1686,7 +1705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1703,7 +1722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1720,7 +1739,7 @@
         <v>42690</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1737,7 +1756,7 @@
         <v>42460</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1754,7 +1773,7 @@
         <v>41963</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1771,7 +1790,7 @@
         <v>41661</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1788,7 +1807,7 @@
         <v>42459</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1808,7 +1827,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -1828,7 +1847,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1848,7 +1867,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -1865,7 +1884,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1882,7 +1901,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1899,7 +1918,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1916,7 +1935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1933,7 +1952,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1950,7 +1969,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -1967,7 +1986,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -1984,7 +2003,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2001,7 +2020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -2010,7 +2029,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -2024,7 +2043,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2041,7 +2060,7 @@
         <v>43783</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -2061,7 +2080,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2078,7 +2097,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2092,7 +2111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -2112,7 +2131,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2132,7 +2151,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2149,7 +2168,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -2166,7 +2185,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -2183,7 +2202,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -2203,7 +2222,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -2223,7 +2242,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -2237,7 +2256,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>163</v>
       </c>
@@ -2254,7 +2273,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -2271,7 +2290,7 @@
         <v>43481</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2288,7 +2307,7 @@
         <v>42603</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2305,7 +2324,7 @@
         <v>42602</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2322,7 +2341,7 @@
         <v>44151</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -2339,7 +2358,7 @@
         <v>43398</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -2359,7 +2378,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2379,7 +2398,7 @@
         <v>43735</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -2387,7 +2406,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -2395,7 +2414,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -2403,7 +2422,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>35</v>
       </c>
@@ -2423,7 +2442,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -2440,7 +2459,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -2457,7 +2476,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2474,7 +2493,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>35</v>
       </c>
@@ -2494,7 +2513,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -2502,7 +2521,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -2519,7 +2538,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>173</v>
       </c>
@@ -2536,7 +2555,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -2550,7 +2569,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -2558,7 +2577,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>47</v>
       </c>
@@ -2581,7 +2600,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -2604,7 +2623,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2621,7 +2640,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2638,7 +2657,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -2655,7 +2674,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>69</v>
       </c>
@@ -2663,7 +2682,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>69</v>
       </c>
@@ -2671,7 +2690,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>35</v>
       </c>
@@ -2691,7 +2710,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -2699,7 +2718,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>35</v>
       </c>
@@ -2716,7 +2735,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2733,7 +2752,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -2750,7 +2769,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>163</v>
       </c>
@@ -2767,7 +2786,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -2784,7 +2803,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -2801,7 +2820,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -2818,7 +2837,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -2835,7 +2854,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>44</v>
       </c>
@@ -2852,7 +2871,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>69</v>
       </c>
@@ -2860,7 +2879,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>69</v>
       </c>
@@ -2868,7 +2887,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -2888,7 +2907,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -2908,7 +2927,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>35</v>
       </c>
@@ -2928,7 +2947,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>35</v>
       </c>
@@ -2945,7 +2964,7 @@
         <v>45227</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>69</v>
       </c>
@@ -2953,7 +2972,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>69</v>
       </c>
@@ -2961,7 +2980,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2981,7 +3000,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -3001,7 +3020,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -3021,7 +3040,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -3041,7 +3060,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -3061,7 +3080,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>163</v>
       </c>
@@ -3078,7 +3097,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -3095,7 +3114,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>69</v>
       </c>
@@ -3103,7 +3122,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3123,7 +3142,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -3143,7 +3162,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>69</v>
       </c>
@@ -3151,7 +3170,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>69</v>
       </c>
@@ -3159,7 +3178,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>69</v>
       </c>
@@ -3167,7 +3186,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>44</v>
       </c>
@@ -3181,7 +3200,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -3201,7 +3220,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>69</v>
       </c>
@@ -3209,7 +3228,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>173</v>
       </c>
@@ -3226,7 +3245,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>69</v>
       </c>
@@ -3234,7 +3253,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -3254,7 +3273,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>69</v>
       </c>
@@ -3262,7 +3281,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -3282,7 +3301,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>69</v>
       </c>
@@ -3290,7 +3309,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>44</v>
       </c>
@@ -3307,7 +3326,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>163</v>
       </c>
@@ -3318,7 +3337,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>163</v>
       </c>
@@ -3329,7 +3348,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>163</v>
       </c>
@@ -3340,7 +3359,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>163</v>
       </c>
@@ -3351,7 +3370,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>163</v>
       </c>
@@ -3362,7 +3381,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>163</v>
       </c>
@@ -3373,7 +3392,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>163</v>
       </c>
@@ -3384,7 +3403,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -3395,7 +3414,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>69</v>
       </c>
@@ -3403,7 +3422,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -3423,7 +3442,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3443,7 +3462,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3463,7 +3482,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -3477,7 +3496,7 @@
         <v>45869</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -3497,7 +3516,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -3517,7 +3536,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -3534,7 +3553,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>163</v>
       </c>
@@ -3551,7 +3570,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -3565,7 +3584,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>44</v>
       </c>
@@ -3582,7 +3601,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>47</v>
       </c>
@@ -3605,7 +3624,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>47</v>
       </c>
@@ -3625,7 +3644,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>44</v>
       </c>
@@ -3642,7 +3661,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>44</v>
       </c>
@@ -3659,7 +3678,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>69</v>
       </c>
@@ -3667,7 +3686,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>69</v>
       </c>
@@ -3675,7 +3694,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>129</v>
       </c>
@@ -3692,7 +3711,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -3712,7 +3731,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -3732,7 +3751,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>8</v>
       </c>
@@ -3752,7 +3771,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>8</v>
       </c>
@@ -3772,12 +3791,62 @@
         <v>305</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>69</v>
       </c>
       <c r="B151" t="s">
         <v>307</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" t="s">
+        <v>309</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E152" t="s">
+        <v>308</v>
+      </c>
+      <c r="G152" s="1">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>69</v>
+      </c>
+      <c r="B153" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>69</v>
+      </c>
+      <c r="B154" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>163</v>
+      </c>
+      <c r="B155" t="s">
+        <v>312</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E155" t="s">
+        <v>150</v>
+      </c>
+      <c r="F155" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C4FDA76-7522-4407-9B60-216AB26505CF}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E829ADBF-B46F-4F85-8E24-0FC964F3282A}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-11745" windowWidth="21840" windowHeight="37920" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="314">
   <si>
     <t>type</t>
   </si>
@@ -964,6 +964,9 @@
   </si>
   <si>
     <t>Declan Sullivan</t>
+  </si>
+  <si>
+    <t>British Journal of Criminology</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -3847,6 +3850,14 @@
       </c>
       <c r="F155" t="s">
         <v>220</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>69</v>
+      </c>
+      <c r="B156" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
